--- a/human_resources_forms/044_scouting_recruitment_form--human_resources_forms.xlsx
+++ b/human_resources_forms/044_scouting_recruitment_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>scouting_recruitment_form</t>
+          <t>scouting_recruitment_plan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>scouting_recruitment_plan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the unit's scouting recruitment plan?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Describe the unit's scouting recruitment plan</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the unit's ID?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unit ID</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the unit's name?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unit name</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Unit contact information</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Contact information for the unit</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,17 +628,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>Unit contact email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Contact information for unit</t>
+          <t>Unit contact email</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -634,22 +650,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>unit_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>What is the unit's type?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Contact email</t>
+          <t>Type of unit</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -661,22 +677,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>unit_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Unit level</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Contact phone</t>
+          <t>Unit level</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -688,22 +704,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>unit_type</t>
+          <t>recruitment_goal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unit_type</t>
+          <t>What is the unit's recruitment goal?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Type of unit</t>
+          <t>Recruitment goal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -715,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>unit_type_other</t>
+          <t>target_start_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unit_type</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Target start date</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Target start date for the recruitment campaign</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -738,22 +758,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>unit_level</t>
+          <t>target_end_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unit_level</t>
+          <t>Target end date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Unit level</t>
+          <t>Target end date for the recruitment campaign</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -765,22 +785,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>recruitment_goal</t>
+          <t>event_dates</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>recruitment_goal</t>
+          <t>Dates for events</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Recruitment goal</t>
+          <t>Dates for events related to the recruitment campaign</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -792,22 +812,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>target_start_date</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Target start date</t>
+          <t>Additional notes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -819,22 +839,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>target_end_date</t>
+          <t>recruiter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>Scouting recruiters for the unit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Target end date</t>
+          <t>Scouting recruiters for the unit</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -846,22 +866,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event_dates</t>
+          <t>other_recruiters</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dates</t>
+          <t>Other scouting recruiters</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dates for events</t>
+          <t>Other scouting recruiters for the unit</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -873,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>unit_officer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Unit officer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Unit officer</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -896,160 +920,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>scouting_recruiters</t>
+          <t>flyer_request</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>recruiter</t>
+          <t>Do you need a flyer?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Scouting recruiters for unit</t>
+          <t>Do you need a flyer?</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>other_recruiters</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>recruiter</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Other recruiters</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>unit_officer</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>unit_officer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Unit officer</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>flyer_request</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>request_flyer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Do you need a flyer?</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>flyer_request</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>request_flyer</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Do you need a flyer?</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>flyer_request</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>flyer_request</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Do you need a flyer?</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1066,10 +955,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1179,7 +1068,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>scouting_recruiters_choices</t>
+          <t>recruiter_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1196,7 +1085,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>scouting_recruiters_choices</t>
+          <t>recruiter_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1213,7 +1102,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>scouting_recruiters_choices</t>
+          <t>recruiter_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1269,12 +1158,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1286,78 +1175,10 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>flyer_request_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>flyer_request_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>flyer_request_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>flyer_request_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
